--- a/artfynd/A 45117-2023 artfynd.xlsx
+++ b/artfynd/A 45117-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45117-2023 artfynd.xlsx
+++ b/artfynd/A 45117-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>119865118</v>
       </c>
       <c r="B4" t="n">
-        <v>57226</v>
+        <v>57236</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 45117-2023 artfynd.xlsx
+++ b/artfynd/A 45117-2023 artfynd.xlsx
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121143097</v>
+        <v>121143098</v>
       </c>
       <c r="B5" t="n">
-        <v>5189</v>
+        <v>4766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,21 +1046,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485595</v>
+        <v>485513</v>
       </c>
       <c r="R5" t="n">
-        <v>6539595</v>
+        <v>6539644</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121143098</v>
+        <v>121143097</v>
       </c>
       <c r="B6" t="n">
-        <v>4766</v>
+        <v>5189</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,21 +1163,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485513</v>
+        <v>485595</v>
       </c>
       <c r="R6" t="n">
-        <v>6539644</v>
+        <v>6539595</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 45117-2023 artfynd.xlsx
+++ b/artfynd/A 45117-2023 artfynd.xlsx
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121143098</v>
+        <v>121143097</v>
       </c>
       <c r="B5" t="n">
-        <v>4766</v>
+        <v>5189</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,21 +1046,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485513</v>
+        <v>485595</v>
       </c>
       <c r="R5" t="n">
-        <v>6539644</v>
+        <v>6539595</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121143097</v>
+        <v>121143098</v>
       </c>
       <c r="B6" t="n">
-        <v>5189</v>
+        <v>4766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,21 +1163,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485595</v>
+        <v>485513</v>
       </c>
       <c r="R6" t="n">
-        <v>6539595</v>
+        <v>6539644</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 45117-2023 artfynd.xlsx
+++ b/artfynd/A 45117-2023 artfynd.xlsx
@@ -1033,7 +1033,7 @@
         <v>121143098</v>
       </c>
       <c r="B5" t="n">
-        <v>4766</v>
+        <v>4769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>121143097</v>
       </c>
       <c r="B6" t="n">
-        <v>5189</v>
+        <v>5192</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 45117-2023 artfynd.xlsx
+++ b/artfynd/A 45117-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112684970</v>
+        <v>119865118</v>
       </c>
       <c r="B2" t="n">
-        <v>4758</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100299</v>
+        <v>100067</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>3K+</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Häggen, Nrk</t>
+          <t>Lisselängen, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485544</v>
+        <v>485539</v>
       </c>
       <c r="R2" t="n">
-        <v>6539645</v>
+        <v>6539317</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +754,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-12</t>
+          <t>2024-03-11</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Två subadulta havsörnar (3-4 K) hittas ca 2 km N  från obsplatsen. De rör sig sakta mot SV och passerar obsplatsen på under 1 km avstånd innan de fortsätter mot SV och tappas bakom skogshorisonten. Örnarna parflyger och "leke</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,34 +783,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Petter Bohman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Petter Bohman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112684975</v>
+        <v>112684970</v>
       </c>
       <c r="B3" t="n">
-        <v>5182</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -899,67 +908,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119865118</v>
+        <v>121143098</v>
       </c>
       <c r="B4" t="n">
-        <v>57236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100067</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>3K+</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lisselängen, Nrk</t>
+          <t>Hallsberg-Laxå, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485539</v>
+        <v>485513</v>
       </c>
       <c r="R4" t="n">
-        <v>6539317</v>
+        <v>6539644</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,27 +982,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:13</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-03-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:23</t>
+          <t>2023-10-12</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Två subadulta havsörnar (3-4 K) hittas ca 2 km N  från obsplatsen. De rör sig sakta mot SV och passerar obsplatsen på under 1 km avstånd innan de fortsätter mot SV och tappas bakom skogshorisonten. Örnarna parflyger och "leke</t>
+          <t>kläckhål och/eller gnag</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,33 +1001,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Petter Bohman</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121143098</v>
+        <v>112684975</v>
       </c>
       <c r="B5" t="n">
-        <v>4769</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,21 +1031,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1075,17 +1060,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hallsberg-Laxå, Nrk</t>
+          <t>Häggen, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485513</v>
+        <v>485544</v>
       </c>
       <c r="R5" t="n">
-        <v>6539644</v>
+        <v>6539645</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,11 +1100,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-10-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>kläckhål och/eller gnag</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,12 +1130,7 @@
         <v>121143097</v>
       </c>
       <c r="B6" t="n">
-        <v>5192</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,6 +1237,713 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122939753</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hallsberg-Timmersdala, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>485651</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6538993</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122939754</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hallsberg-Timmersdala, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>485652</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6538993</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122939755</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hallsberg-Timmersdala, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>485655</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6538997</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122939756</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hallsberg-Timmersdala, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>485652</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6538982</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122939758</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hallsberg-Timmersdala, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>485649</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6538977</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122939759</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hallsberg-Timmersdala, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>485636</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6538934</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122939761</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hallsberg-Timmersdala, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>485636</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6538932</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Viby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45117-2023 artfynd.xlsx
+++ b/artfynd/A 45117-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119865118</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112684970</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143098</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112684975</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121143097</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122939753</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122939754</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122939755</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122939756</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,6 +1791,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122939758</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1842,6 +1897,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122939759</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1943,8 +2003,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122939761</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>